--- a/assessment_forms/037_lead_acid_battery_safety_assessment--assessment_forms.xlsx
+++ b/assessment_forms/037_lead_acid_battery_safety_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'12v'}</t>
+          <t>12v</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '12V'}</t>
+          <t>12V</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'6v'}</t>
+          <t>6v</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '6V'}</t>
+          <t>6V</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'not_started',_'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Not Started', 'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'scheduled',_'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Scheduled', 'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress',_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress', 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'n/a',_'label':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'N/A', 'label': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'basement',_'label':_'basement'}</t>
+          <t>basement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Basement', 'label': 'Basement'}</t>
+          <t>Basement</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse',_'label':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse', 'label': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'correctly',_'label':_'correctly'}</t>
+          <t>correctly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Correctly', 'label': 'Correctly'}</t>
+          <t>Correctly</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'incorrectly',_'label':_'incorrectly'}</t>
+          <t>incorrectly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Incorrectly', 'label': 'Incorrectly'}</t>
+          <t>Incorrectly</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
